--- a/astro-site/public/dl/guia-pasteleria-obrador/estacionalidad-y-picos.xlsx
+++ b/astro-site/public/dl/guia-pasteleria-obrador/estacionalidad-y-picos.xlsx
@@ -1573,23 +1573,23 @@
         <v>0</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>420</v>
+        <v>160</v>
       </c>
       <c r="L6" s="20">
         <f>IFERROR(K6-J6,"")</f>
-        <v>420.0</v>
+        <v>160.0</v>
       </c>
       <c r="M6" s="20">
         <f>IFERROR(K6*E6,"")</f>
-        <v>2100.0</v>
+        <v>800.0</v>
       </c>
       <c r="N6" s="19">
         <f>IFERROR(M6*I6,"")</f>
-        <v>31499.999999999996</v>
+        <v>11999.999999999998</v>
       </c>
       <c r="O6" s="19">
         <f>IFERROR(L6*E6*I6,"")</f>
-        <v>31499.999999999996</v>
+        <v>11999.999999999998</v>
       </c>
       <c r="P6" s="13" t="n">
         <v>6</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="R6" s="21" t="inlineStr">
         <is>
-          <t>El pico que decide el año. Referencias de escala, nunca de precio ni de cuota: PS-35 (unos 30 millones de roscones en España en la campaña 2025/26), PS-36 (más de 2,9 millones en la Comunidad de Madrid) y PS-38 (El Corte Inglés 850.000, Viena Capellanes 72.000). PS-46: el supermercado entra con roscones premiados a 9 €. El roscón relleno de nata arrastra los 4 °C de la fila 9 y las 24 h del art. 9.3 justo el día de más producción: eso limita la producción tanto como el horno.</t>
+          <t>El pico que decide el año. Las unidades de campaña son las de los CINCO días de más venta: 160 al día, 800 en total, el 47 % de los roscones que el mix de la carta asigna al año (1,2 % de las piezas). El resto se venden en la semana previa, fuera de la ventana de campaña, y por eso no entran en esta fila. Referencias de escala, nunca de precio ni de cuota: PS-35 (unos 30 millones de roscones en España en la campaña 2025/26), PS-36 (más de 2,9 millones en la Comunidad de Madrid) y PS-38 (El Corte Inglés 850.000, Viena Capellanes 72.000). PS-46: el supermercado entra con roscones premiados a 9 €. El roscón relleno de nata arrastra los 4 °C de la fila 9 y las 24 h del art. 9.3 justo el día de más producción: eso limita la producción tanto como el horno.</t>
         </is>
       </c>
     </row>
@@ -1780,23 +1780,23 @@
         <v>0</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="L9" s="20">
         <f>IFERROR(K9-J9,"")</f>
-        <v>240.0</v>
+        <v>230.0</v>
       </c>
       <c r="M9" s="20">
         <f>IFERROR(K9*E9,"")</f>
-        <v>1920.0</v>
+        <v>1840.0</v>
       </c>
       <c r="N9" s="19">
         <f>IFERROR(M9*I9,"")</f>
-        <v>4189.090909090909</v>
+        <v>4014.545454545454</v>
       </c>
       <c r="O9" s="19">
         <f>IFERROR(L9*E9*I9,"")</f>
-        <v>4189.090909090909</v>
+        <v>4014.545454545454</v>
       </c>
       <c r="P9" s="13" t="n">
         <v>2.4</v>
@@ -1806,7 +1806,7 @@
       </c>
       <c r="R9" s="21" t="inlineStr">
         <is>
-          <t>Ocho días seguidos de producción extra, que es más agotador que los cinco de Reyes aunque el pico sea menor. Torrijas y monas a la vez: una necesita freidora y frío, la otra horno y chocolate.</t>
+          <t>Ocho días seguidos de producción extra, que es más agotador que los cinco de Reyes aunque el pico sea menor. Torrijas y monas a la vez: una necesita freidora y frío, la otra horno y chocolate. Son 230 torrijas al día y 1.840 en la campaña: el 99 % de las que el mix de la carta asigna al año, porque fuera de Semana Santa no se hacen.</t>
         </is>
       </c>
     </row>
@@ -1918,23 +1918,23 @@
         <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
-        <v>520</v>
+        <v>470</v>
       </c>
       <c r="L11" s="20">
         <f>IFERROR(K11-J11,"")</f>
-        <v>520.0</v>
+        <v>470.0</v>
       </c>
       <c r="M11" s="20">
         <f>IFERROR(K11*E11,"")</f>
-        <v>1560.0</v>
+        <v>1410.0</v>
       </c>
       <c r="N11" s="19">
         <f>IFERROR(M11*I11,"")</f>
-        <v>2269.090909090909</v>
+        <v>2050.909090909091</v>
       </c>
       <c r="O11" s="19">
         <f>IFERROR(L11*E11*I11,"")</f>
-        <v>2269.090909090909</v>
+        <v>2050.909090909091</v>
       </c>
       <c r="P11" s="13" t="n">
         <v>2.6</v>
@@ -1944,7 +1944,7 @@
       </c>
       <c r="R11" s="21" t="inlineStr">
         <is>
-          <t>Tres días con tres referencias que sólo se hacen ahora: buñuelos, huesos de santo y panellets. Los buñuelos van rellenos (4 °C y 24 h) y los otros dos son estables a temperatura ambiente: por eso los buñuelos se hacen el mismo día y los huesos de santo se pueden adelantar. Ese detalle legal ES la planificación de la campaña.</t>
+          <t>Tres días con tres referencias que sólo se hacen ahora: buñuelos, huesos de santo y panellets. Los buñuelos van rellenos (4 °C y 24 h) y los otros dos son estables a temperatura ambiente: por eso los buñuelos se hacen el mismo día y los huesos de santo se pueden adelantar. Ese detalle legal ES la planificación de la campaña. Son 470 buñuelos al día y 1.410 en los tres días: el 99 % de los que el mix de la carta asigna al año, porque fuera de esta fecha no se hacen.</t>
         </is>
       </c>
     </row>
@@ -1961,15 +1961,15 @@
       </c>
       <c r="M13" s="15">
         <f>SUM(M6:M11)</f>
-        <v>7164.0</v>
+        <v>5634.0</v>
       </c>
       <c r="N13" s="17">
         <f>SUM(N6:N11)</f>
-        <v>42371.27272727273</v>
+        <v>22478.545454545452</v>
       </c>
       <c r="O13" s="17">
         <f>SUM(O6:O11)</f>
-        <v>41162.72727272727</v>
+        <v>21270.0</v>
       </c>
     </row>
     <row r="14"/>
@@ -2098,15 +2098,15 @@
         </is>
       </c>
       <c r="B6" s="23" t="n">
-        <v>1.18</v>
+        <v>1.34</v>
       </c>
       <c r="C6" s="19">
         <f>IFERROR('Parámetros'!$B$6*B6/$B$18,"")</f>
-        <v>31682.79054999999</v>
+        <v>35978.76215</v>
       </c>
       <c r="D6" s="24">
         <f>IFERROR(C6/'Parámetros'!$B$6,"")</f>
-        <v>0.0983333333333333</v>
+        <v>0.11166666666666668</v>
       </c>
       <c r="E6" s="5" t="inlineStr">
         <is>
@@ -2126,15 +2126,15 @@
         </is>
       </c>
       <c r="B7" s="23" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.93</v>
       </c>
       <c r="C7" s="19">
         <f>IFERROR('Parámetros'!$B$6*B7/$B$18,"")</f>
-        <v>25238.83314999999</v>
+        <v>24970.334925000003</v>
       </c>
       <c r="D7" s="24">
         <f>IFERROR(C7/'Parámetros'!$B$6,"")</f>
-        <v>0.07833333333333331</v>
+        <v>0.07750000000000001</v>
       </c>
       <c r="E7" s="5" t="inlineStr">
         <is>
@@ -2154,15 +2154,15 @@
         </is>
       </c>
       <c r="B8" s="23" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="C8" s="19">
         <f>IFERROR('Parámetros'!$B$6*B8/$B$18,"")</f>
-        <v>26312.826049999996</v>
+        <v>26044.327825</v>
       </c>
       <c r="D8" s="24">
         <f>IFERROR(C8/'Parámetros'!$B$6,"")</f>
-        <v>0.08166666666666665</v>
+        <v>0.08083333333333334</v>
       </c>
       <c r="E8" s="5" t="inlineStr">
         <is>
@@ -2182,15 +2182,15 @@
         </is>
       </c>
       <c r="B9" s="23" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="C9" s="19">
         <f>IFERROR('Parámetros'!$B$6*B9/$B$18,"")</f>
-        <v>28192.313624999995</v>
+        <v>27923.815400000003</v>
       </c>
       <c r="D9" s="24">
         <f>IFERROR(C9/'Parámetros'!$B$6,"")</f>
-        <v>0.08749999999999998</v>
+        <v>0.08666666666666668</v>
       </c>
       <c r="E9" s="5" t="inlineStr">
         <is>
@@ -2210,15 +2210,15 @@
         </is>
       </c>
       <c r="B10" s="23" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="C10" s="19">
         <f>IFERROR('Parámetros'!$B$6*B10/$B$18,"")</f>
-        <v>28997.808299999993</v>
+        <v>28729.310075</v>
       </c>
       <c r="D10" s="24">
         <f>IFERROR(C10/'Parámetros'!$B$6,"")</f>
-        <v>0.08999999999999998</v>
+        <v>0.08916666666666667</v>
       </c>
       <c r="E10" s="5" t="inlineStr">
         <is>
@@ -2238,15 +2238,15 @@
         </is>
       </c>
       <c r="B11" s="23" t="n">
-        <v>0.98</v>
+        <v>0.97</v>
       </c>
       <c r="C11" s="19">
         <f>IFERROR('Parámetros'!$B$6*B11/$B$18,"")</f>
-        <v>26312.826049999996</v>
+        <v>26044.327825</v>
       </c>
       <c r="D11" s="24">
         <f>IFERROR(C11/'Parámetros'!$B$6,"")</f>
-        <v>0.08166666666666665</v>
+        <v>0.08083333333333334</v>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
@@ -2266,15 +2266,15 @@
         </is>
       </c>
       <c r="B12" s="23" t="n">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="C12" s="19">
         <f>IFERROR('Parámetros'!$B$6*B12/$B$18,"")</f>
-        <v>23090.847349999996</v>
+        <v>22822.349124999997</v>
       </c>
       <c r="D12" s="24">
         <f>IFERROR(C12/'Parámetros'!$B$6,"")</f>
-        <v>0.07166666666666666</v>
+        <v>0.07083333333333333</v>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
@@ -2294,15 +2294,15 @@
         </is>
       </c>
       <c r="B13" s="23" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="C13" s="19">
         <f>IFERROR('Parámetros'!$B$6*B13/$B$18,"")</f>
-        <v>18257.879299999997</v>
+        <v>17452.384625000002</v>
       </c>
       <c r="D13" s="24">
         <f>IFERROR(C13/'Parámetros'!$B$6,"")</f>
-        <v>0.05666666666666666</v>
+        <v>0.054166666666666675</v>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
@@ -2322,15 +2322,15 @@
         </is>
       </c>
       <c r="B14" s="23" t="n">
-        <v>0.92</v>
+        <v>0.91</v>
       </c>
       <c r="C14" s="19">
         <f>IFERROR('Parámetros'!$B$6*B14/$B$18,"")</f>
-        <v>24701.836699999996</v>
+        <v>24433.338475</v>
       </c>
       <c r="D14" s="24">
         <f>IFERROR(C14/'Parámetros'!$B$6,"")</f>
-        <v>0.07666666666666666</v>
+        <v>0.07583333333333334</v>
       </c>
       <c r="E14" s="5" t="inlineStr">
         <is>
@@ -2350,15 +2350,15 @@
         </is>
       </c>
       <c r="B15" s="23" t="n">
-        <v>0.96</v>
+        <v>0.95</v>
       </c>
       <c r="C15" s="19">
         <f>IFERROR('Parámetros'!$B$6*B15/$B$18,"")</f>
-        <v>25775.829599999994</v>
+        <v>25507.331374999998</v>
       </c>
       <c r="D15" s="24">
         <f>IFERROR(C15/'Parámetros'!$B$6,"")</f>
-        <v>0.07999999999999999</v>
+        <v>0.07916666666666666</v>
       </c>
       <c r="E15" s="5" t="inlineStr">
         <is>
@@ -2378,15 +2378,15 @@
         </is>
       </c>
       <c r="B16" s="23" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="C16" s="19">
         <f>IFERROR('Parámetros'!$B$6*B16/$B$18,"")</f>
-        <v>29266.306524999996</v>
+        <v>28997.8083</v>
       </c>
       <c r="D16" s="24">
         <f>IFERROR(C16/'Parámetros'!$B$6,"")</f>
-        <v>0.09083333333333332</v>
+        <v>0.09</v>
       </c>
       <c r="E16" s="5" t="inlineStr">
         <is>
@@ -2406,15 +2406,15 @@
         </is>
       </c>
       <c r="B17" s="23" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="C17" s="19">
         <f>IFERROR('Parámetros'!$B$6*B17/$B$18,"")</f>
-        <v>34367.7728</v>
+        <v>33293.7799</v>
       </c>
       <c r="D17" s="24">
         <f>IFERROR(C17/'Parámetros'!$B$6,"")</f>
-        <v>0.10666666666666666</v>
+        <v>0.10333333333333333</v>
       </c>
       <c r="E17" s="5" t="inlineStr">
         <is>
@@ -2435,15 +2435,15 @@
       </c>
       <c r="B18" s="25">
         <f>SUM(B6:B17)</f>
-        <v>12.000000000000002</v>
+        <v>12.0</v>
       </c>
       <c r="C18" s="17">
         <f>SUM(C6:C17)</f>
-        <v>322197.86999999994</v>
+        <v>322197.87000000005</v>
       </c>
       <c r="D18" s="26">
         <f>SUM(D6:D17)</f>
-        <v>0.9999999999999998</v>
+        <v>1.0</v>
       </c>
       <c r="F18" s="22" t="inlineStr">
         <is>
@@ -2520,23 +2520,23 @@
       </c>
       <c r="C24" s="19">
         <f>'Calendario de 6 Picos'!N6</f>
-        <v>31499.999999999996</v>
+        <v>11999.999999999998</v>
       </c>
       <c r="D24" s="24">
         <f>IFERROR(C24/'Parámetros'!$B$6,"")</f>
-        <v>0.09776600944009964</v>
+        <v>0.03724419407241891</v>
       </c>
       <c r="E24" s="19">
         <f>'Calendario de 6 Picos'!O6</f>
-        <v>31499.999999999996</v>
+        <v>11999.999999999998</v>
       </c>
       <c r="F24" s="24">
         <f>IFERROR(E24/'Parámetros'!$B$6,"")</f>
-        <v>0.09776600944009964</v>
+        <v>0.03724419407241891</v>
       </c>
       <c r="G24" s="19">
         <f>IFERROR(C24/B24,"")</f>
-        <v>6299.999999999999</v>
+        <v>2399.9999999999995</v>
       </c>
       <c r="H24" s="19">
         <f>IFERROR('Parámetros'!$B$6/'Parámetros'!$B$8,"")</f>
@@ -2544,7 +2544,7 @@
       </c>
       <c r="I24" s="27">
         <f>IFERROR(G24/H24,"")</f>
-        <v>5.865960566405978</v>
+        <v>2.2346516443451345</v>
       </c>
     </row>
     <row r="25">
@@ -2637,23 +2637,23 @@
       </c>
       <c r="C27" s="19">
         <f>'Calendario de 6 Picos'!N9</f>
-        <v>4189.090909090909</v>
+        <v>4014.545454545454</v>
       </c>
       <c r="D27" s="24">
         <f>IFERROR(C27/'Parámetros'!$B$6,"")</f>
-        <v>0.013001609567098966</v>
+        <v>0.012459875835136509</v>
       </c>
       <c r="E27" s="19">
         <f>'Calendario de 6 Picos'!O9</f>
-        <v>4189.090909090909</v>
+        <v>4014.545454545454</v>
       </c>
       <c r="F27" s="24">
         <f>IFERROR(E27/'Parámetros'!$B$6,"")</f>
-        <v>0.013001609567098966</v>
+        <v>0.012459875835136509</v>
       </c>
       <c r="G27" s="19">
         <f>IFERROR(C27/B27,"")</f>
-        <v>523.6363636363636</v>
+        <v>501.81818181818176</v>
       </c>
       <c r="H27" s="19">
         <f>IFERROR('Parámetros'!$B$6/'Parámetros'!$B$8,"")</f>
@@ -2661,7 +2661,7 @@
       </c>
       <c r="I27" s="27">
         <f>IFERROR(G27/H27,"")</f>
-        <v>0.48756035876621123</v>
+        <v>0.46724534381761906</v>
       </c>
     </row>
     <row r="28">
@@ -2715,23 +2715,23 @@
       </c>
       <c r="C29" s="19">
         <f>'Calendario de 6 Picos'!N11</f>
-        <v>2269.090909090909</v>
+        <v>2050.909090909091</v>
       </c>
       <c r="D29" s="24">
         <f>IFERROR(C29/'Parámetros'!$B$6,"")</f>
-        <v>0.00704253851551194</v>
+        <v>0.006365371350558869</v>
       </c>
       <c r="E29" s="19">
         <f>'Calendario de 6 Picos'!O11</f>
-        <v>2269.090909090909</v>
+        <v>2050.909090909091</v>
       </c>
       <c r="F29" s="24">
         <f>IFERROR(E29/'Parámetros'!$B$6,"")</f>
-        <v>0.00704253851551194</v>
+        <v>0.006365371350558869</v>
       </c>
       <c r="G29" s="19">
         <f>IFERROR(C29/B29,"")</f>
-        <v>756.3636363636364</v>
+        <v>683.6363636363636</v>
       </c>
       <c r="H29" s="19">
         <f>IFERROR('Parámetros'!$B$6/'Parámetros'!$B$8,"")</f>
@@ -2739,7 +2739,7 @@
       </c>
       <c r="I29" s="27">
         <f>IFERROR(G29/H29,"")</f>
-        <v>0.704253851551194</v>
+        <v>0.6365371350558869</v>
       </c>
     </row>
     <row r="30">
@@ -2754,19 +2754,19 @@
       </c>
       <c r="C30" s="17">
         <f>SUM(C24:C29)</f>
-        <v>42371.27272727273</v>
+        <v>22478.545454545452</v>
       </c>
       <c r="D30" s="26">
         <f>SUM(D24:D29)</f>
-        <v>0.131506992045828</v>
+        <v>0.06976627578123173</v>
       </c>
       <c r="E30" s="17">
         <f>SUM(E24:E29)</f>
-        <v>41162.72727272727</v>
+        <v>21270.0</v>
       </c>
       <c r="F30" s="26">
         <f>SUM(F24:F29)</f>
-        <v>0.12775605025795878</v>
+        <v>0.06601533399336253</v>
       </c>
     </row>
     <row r="31"/>
@@ -3655,11 +3655,11 @@
       </c>
       <c r="J6" s="20">
         <f>'Calendario de 6 Picos'!M6</f>
-        <v>2100.0</v>
+        <v>800.0</v>
       </c>
       <c r="K6" s="19">
         <f>IFERROR(I6*J6,"")</f>
-        <v>5457.4800000000005</v>
+        <v>2079.04</v>
       </c>
       <c r="L6" s="20">
         <f>'Calendario de 6 Picos'!Q6</f>
@@ -3671,19 +3671,19 @@
       </c>
       <c r="N6" s="19">
         <f>IFERROR(K6*'Parámetros'!$B$24*M6/365,"")</f>
-        <v>43.570128000000004</v>
+        <v>16.598143999999998</v>
       </c>
       <c r="O6" s="19">
         <f>IFERROR(I6*'Calendario de 6 Picos'!L6*'Calendario de 6 Picos'!E6,"")</f>
-        <v>5457.4800000000005</v>
+        <v>2079.0400000000004</v>
       </c>
       <c r="P6" s="19">
         <f>'Calendario de 6 Picos'!O6</f>
-        <v>31499.999999999996</v>
+        <v>11999.999999999998</v>
       </c>
       <c r="Q6" s="19">
         <f>IFERROR(P6-O6-F6-N6,"")</f>
-        <v>24395.21196188764</v>
+        <v>8300.623945887637</v>
       </c>
       <c r="R6" s="21" t="inlineStr">
         <is>
@@ -3874,11 +3874,11 @@
       </c>
       <c r="J9" s="20">
         <f>'Calendario de 6 Picos'!M9</f>
-        <v>1920.0</v>
+        <v>1840.0</v>
       </c>
       <c r="K9" s="19">
         <f>IFERROR(I9*J9,"")</f>
-        <v>499.392</v>
+        <v>478.584</v>
       </c>
       <c r="L9" s="20">
         <f>'Calendario de 6 Picos'!Q9</f>
@@ -3890,19 +3890,19 @@
       </c>
       <c r="N9" s="19">
         <f>IFERROR(K9*'Parámetros'!$B$24*M9/365,"")</f>
-        <v>3.0538162849315067</v>
+        <v>2.9265739397260275</v>
       </c>
       <c r="O9" s="19">
         <f>IFERROR(I9*'Calendario de 6 Picos'!L9*'Calendario de 6 Picos'!E9,"")</f>
-        <v>499.392</v>
+        <v>478.584</v>
       </c>
       <c r="P9" s="19">
         <f>'Calendario de 6 Picos'!O9</f>
-        <v>4189.090909090909</v>
+        <v>4014.545454545454</v>
       </c>
       <c r="Q9" s="19">
         <f>IFERROR(P9-O9-F9-N9,"")</f>
-        <v>3152.0657894351907</v>
+        <v>2998.4555772349413</v>
       </c>
       <c r="R9" s="21" t="inlineStr">
         <is>
@@ -4020,11 +4020,11 @@
       </c>
       <c r="J11" s="20">
         <f>'Calendario de 6 Picos'!M11</f>
-        <v>1560.0</v>
+        <v>1410.0</v>
       </c>
       <c r="K11" s="19">
         <f>IFERROR(I11*J11,"")</f>
-        <v>264.42</v>
+        <v>238.995</v>
       </c>
       <c r="L11" s="20">
         <f>'Calendario de 6 Picos'!Q11</f>
@@ -4036,19 +4036,19 @@
       </c>
       <c r="N11" s="19">
         <f>IFERROR(K11*'Parámetros'!$B$24*M11/365,"")</f>
-        <v>1.3923705205479453</v>
+        <v>1.2584887397260274</v>
       </c>
       <c r="O11" s="19">
         <f>IFERROR(I11*'Calendario de 6 Picos'!L11*'Calendario de 6 Picos'!E11,"")</f>
-        <v>264.42</v>
+        <v>238.995</v>
       </c>
       <c r="P11" s="19">
         <f>'Calendario de 6 Picos'!O11</f>
-        <v>2269.090909090909</v>
+        <v>2050.909090909091</v>
       </c>
       <c r="Q11" s="19">
         <f>IFERROR(P11-O11-F11-N11,"")</f>
-        <v>1361.783374525417</v>
+        <v>1169.160438124421</v>
       </c>
       <c r="R11" s="21" t="inlineStr">
         <is>
@@ -4082,23 +4082,23 @@
       </c>
       <c r="K13" s="17">
         <f>SUM(K6:K11)</f>
-        <v>7281.6672</v>
+        <v>3856.9941999999996</v>
       </c>
       <c r="N13" s="17">
         <f>SUM(N6:N11)</f>
-        <v>55.112576613698636</v>
+        <v>27.879468487671225</v>
       </c>
       <c r="O13" s="17">
         <f>SUM(O6:O11)</f>
-        <v>7018.905000000001</v>
+        <v>3594.232</v>
       </c>
       <c r="P13" s="17">
         <f>SUM(P6:P11)</f>
-        <v>41162.72727272727</v>
+        <v>21270.0</v>
       </c>
       <c r="Q13" s="17">
         <f>SUM(Q6:Q11)</f>
-        <v>30293.196642180985</v>
+        <v>13852.37547757974</v>
       </c>
     </row>
     <row r="14"/>
